--- a/artfynd/A 23808-2026 artfynd.xlsx
+++ b/artfynd/A 23808-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136482504</v>
       </c>
       <c r="B4" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23808-2026 artfynd.xlsx
+++ b/artfynd/A 23808-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136482504</v>
       </c>
       <c r="B4" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23808-2026 artfynd.xlsx
+++ b/artfynd/A 23808-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136482504</v>
       </c>
       <c r="B4" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23808-2026 artfynd.xlsx
+++ b/artfynd/A 23808-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136482504</v>
       </c>
       <c r="B4" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23808-2026 artfynd.xlsx
+++ b/artfynd/A 23808-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136482504</v>
       </c>
       <c r="B4" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23808-2026 artfynd.xlsx
+++ b/artfynd/A 23808-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136482504</v>
       </c>
       <c r="B4" t="n">
-        <v>80600</v>
+        <v>80650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23808-2026 artfynd.xlsx
+++ b/artfynd/A 23808-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136482504</v>
       </c>
       <c r="B4" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
